--- a/jogos_2025-06-21.xlsx
+++ b/jogos_2025-06-21.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Mt Druitt Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.13</v>
+        <v>3.03</v>
       </c>
       <c r="M4" t="n">
-        <v>2.84</v>
+        <v>3.74</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>1.99</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.55</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC4" t="n">
         <v>1.5</v>
       </c>
-      <c r="X4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['9', '16', '45']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['4', '36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45829.16666666666</v>
@@ -1030,16 +1030,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mt Druitt Town</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1056,49 +1056,49 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="N5" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
         <v>2.3</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.5</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="n">
         <v>2.38</v>
@@ -1107,32 +1107,32 @@
         <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AD5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['30', '50']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2.4</v>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['24']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45829.16666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="M7" t="n">
-        <v>3.19</v>
+        <v>2.84</v>
       </c>
       <c r="N7" t="n">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['43', '51', '86']</t>
+          <t>['9', '16', '45']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['4', '36']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45829.16666666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
         <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="X8" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['30', '50']</t>
+          <t>['43', '51', '86']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.21</v>
+        <v>1.72</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45829.16666666666</v>
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.27</v>
+        <v>2.81</v>
       </c>
       <c r="M11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.14</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.29</v>
-      </c>
       <c r="U11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.32</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.36</v>
       </c>
       <c r="X11" t="n">
         <v>2.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['46', '65']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['49', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45829.25</v>
@@ -1933,20 +1933,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.81</v>
+        <v>2.27</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.24</v>
+        <v>2.77</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
         <v>2.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['46', '65']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '86']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45829.25</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>7.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>2.72</v>
+        <v>3.31</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.55</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.34</v>
+        <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.81</v>
       </c>
-      <c r="AD14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>['27', '65']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.8</v>
+        <v>3.02</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.56</v>
+        <v>3.75</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45829.29166666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.64</v>
+        <v>4.33</v>
       </c>
       <c r="M15" t="n">
-        <v>3.38</v>
+        <v>3.72</v>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>4.85</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['17', '59', '63', '84']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['22', '49', '9004']</t>
+          <t>['41', '57']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.52</v>
+        <v>2.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>2.73</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45829.29166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>3.72</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.72</v>
+        <v>4.33</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
+          <t>['45', '74', '78']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['24']</t>
-        </is>
-      </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45829.29166666666</v>
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.06</v>
+        <v>3.58</v>
       </c>
       <c r="M17" t="n">
-        <v>3.11</v>
+        <v>3.29</v>
       </c>
       <c r="N17" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="O17" t="n">
-        <v>3.64</v>
+        <v>4.56</v>
       </c>
       <c r="P17" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="T17" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
         <v>1.95</v>
       </c>
       <c r="Z17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['5', '76']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.81</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45829.29166666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.22</v>
+        <v>3.06</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>3.11</v>
       </c>
       <c r="N18" t="n">
-        <v>3.12</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>3.64</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="X18" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
         <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['5', '76']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45829.29166666666</v>
@@ -2836,109 +2836,109 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.3</v>
       </c>
-      <c r="X19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['10', '52']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45829.29166666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O20" t="n">
         <v>3</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.45</v>
       </c>
       <c r="P20" t="n">
         <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['45', '74', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45829.29166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="N21" t="n">
-        <v>3.07</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['19', '31', '74']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['24', '53', '84']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45829.29166666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.33</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N22" t="n">
         <v>3.72</v>
       </c>
-      <c r="N22" t="n">
-        <v>1.61</v>
-      </c>
       <c r="O22" t="n">
-        <v>4.85</v>
+        <v>2.78</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="Q22" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.19</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.04</v>
-      </c>
       <c r="T22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y22" t="n">
         <v>2.65</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.77</v>
-      </c>
       <c r="Z22" t="n">
-        <v>1.93</v>
+        <v>1.41</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.92</v>
+        <v>6.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['17', '59', '63', '84']</t>
+          <t>['16', '54']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['41', '57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>2.09</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.15</v>
+        <v>1.72</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.73</v>
+        <v>1.7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.49</v>
+        <v>2.74</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45829.29166666666</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>2.72</v>
+        <v>3.38</v>
       </c>
       <c r="N23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.72</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.05</v>
-      </c>
       <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.63</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.48</v>
+        <v>2.09</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['16', '54']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45829.29166666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="M24" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['22', '49', '9004']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI24" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['63', '9001']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['9008']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>2.88</v>
+        <v>1.88</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45829.29166666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.38</v>
+        <v>2.42</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3</v>
+        <v>3.06</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>2.63</v>
       </c>
       <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z25" t="n">
         <v>1.79</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AA25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['10', '52']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.5</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AI25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AD25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['27', '65']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45829.29166666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,43 +3765,43 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.58</v>
+        <v>2.67</v>
       </c>
       <c r="M26" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="N26" t="n">
-        <v>1.86</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
-        <v>4.56</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
         <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Y26" t="n">
         <v>1.95</v>
@@ -3810,38 +3810,38 @@
         <v>1.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4502']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45829.29166666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3894,49 +3894,49 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2.48</v>
+        <v>3.07</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W27" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X27" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AA27" t="n">
         <v>4.2</v>
@@ -3945,32 +3945,32 @@
         <v>1.22</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['19', '31', '74']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['24', '53', '84']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['4502']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['25']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45829.29166666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,16 +3997,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.73</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y28" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63', '9001']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['9008']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45829.29166666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O34" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="P34" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.3</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.84</v>
-      </c>
       <c r="AA34" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['22', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['72', '70']</t>
+          <t>['29', '84', '73']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45829.375</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O35" t="n">
-        <v>4.01</v>
+        <v>3.96</v>
       </c>
       <c r="P35" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S35" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="T35" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="U35" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '90+2']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['29', '84', '73']</t>
+          <t>['72', '70']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45829.375</v>
@@ -5287,16 +5287,16 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U38" t="n">
         <v>1.36</v>
       </c>
-      <c r="M38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N38" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V38" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W38" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X38" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="Z38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['63', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.88</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,16 +5416,16 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -5442,65 +5442,65 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.75</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="N39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['63', '90+2']</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="M40" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>2.78</v>
+        <v>3.45</v>
       </c>
       <c r="O40" t="n">
-        <v>2.9</v>
+        <v>2.51</v>
       </c>
       <c r="P40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD40" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q40" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['6', '1', '26', '69', '83', '65']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45829.45833333334</v>
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="M42" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S42" t="n">
         <v>3.8</v>
       </c>
-      <c r="N42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T42" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U42" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>4.35</v>
+        <v>5.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['14', '69', '58', '71', '51']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI42" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45829.45833333334</v>
@@ -5932,22 +5932,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.01</v>
+        <v>2.33</v>
       </c>
       <c r="M43" t="n">
-        <v>3.68</v>
+        <v>3.21</v>
       </c>
       <c r="N43" t="n">
-        <v>3.03</v>
+        <v>2.78</v>
       </c>
       <c r="O43" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P43" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="R43" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="S43" t="n">
-        <v>3.8</v>
+        <v>3.11</v>
       </c>
       <c r="T43" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U43" t="n">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X43" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="Z43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['14', '69', '58', '71', '51']</t>
+          <t>['6', '1', '26', '69', '83', '65']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45829.45833333334</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,23 +6061,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>2</v>
       </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1</v>
-      </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="M44" t="n">
-        <v>4.08</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>5.79</v>
+        <v>2.99</v>
       </c>
       <c r="O44" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="R44" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="T44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD44" t="n">
         <v>2.05</v>
       </c>
-      <c r="U44" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X44" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD44" t="n">
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['6', '36', '90+7']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['42', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH44" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AJ44" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45829.5</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,19 +6190,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="M45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N45" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X45" t="n">
         <v>3.9</v>
       </c>
-      <c r="N45" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X45" t="n">
-        <v>3.2</v>
-      </c>
       <c r="Y45" t="n">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AA45" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
       <c r="AG45" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45829.5</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="M46" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="N46" t="n">
-        <v>7.2</v>
+        <v>11.83</v>
       </c>
       <c r="O46" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="P46" t="n">
         <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>8.449999999999999</v>
+        <v>8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="U46" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X46" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AC46" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['19', '72']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45829.5</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,103 +6448,103 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>11.83</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['19', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,109 +6577,109 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P48" t="n">
         <v>3</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
+        <v>7</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T48" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U48" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="V48" t="n">
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X48" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.65</v>
+        <v>3.25</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['6', '36', '90+7']</t>
+          <t>['42', '90+1']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.52</v>
+        <v>2.45</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45829.5</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="M53" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="O53" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="P53" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.75</v>
+        <v>3.72</v>
       </c>
       <c r="R53" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S53" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="T53" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U53" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W53" t="n">
         <v>1.28</v>
       </c>
       <c r="X53" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7311,20 +7311,20 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['42', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AI53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ53" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45829.5625</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="M54" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="O54" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="P54" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.72</v>
+        <v>2.75</v>
       </c>
       <c r="R54" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S54" t="n">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="T54" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U54" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V54" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W54" t="n">
         <v>1.28</v>
       </c>
       <c r="X54" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AD54" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7440,20 +7440,20 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '87']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45829.5625</v>
@@ -7480,22 +7480,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>NC Magra</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -7506,65 +7506,65 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="M55" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="N55" t="n">
+        <v>12</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X55" t="n">
         <v>4.2</v>
       </c>
-      <c r="N55" t="n">
-        <v>8</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>8</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X55" t="n">
-        <v>3.14</v>
-      </c>
       <c r="Y55" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AH55" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7609,25 +7609,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NC Magra</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -7635,77 +7635,77 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.15</v>
+        <v>3.05</v>
       </c>
       <c r="M56" t="n">
-        <v>6.21</v>
+        <v>2.96</v>
       </c>
       <c r="N56" t="n">
-        <v>12</v>
+        <v>2.21</v>
       </c>
       <c r="O56" t="n">
-        <v>1.55</v>
+        <v>4.7</v>
       </c>
       <c r="P56" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>14.4</v>
+        <v>2.3</v>
       </c>
       <c r="R56" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="S56" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="T56" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="U56" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="V56" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="W56" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X56" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.35</v>
+        <v>3.84</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '17', '77']</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="AH56" t="n">
-        <v>4.8</v>
+        <v>1.22</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7738,25 +7738,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,77 +7764,77 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.05</v>
+        <v>6.83</v>
       </c>
       <c r="M57" t="n">
-        <v>2.96</v>
+        <v>3.76</v>
       </c>
       <c r="N57" t="n">
-        <v>2.21</v>
+        <v>1.48</v>
       </c>
       <c r="O57" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="P57" t="n">
         <v>2.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="R57" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S57" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T57" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U57" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V57" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W57" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X57" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['3', '17', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.94</v>
+        <v>1.18</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7867,22 +7867,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7893,77 +7893,77 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>6.83</v>
+        <v>1.33</v>
       </c>
       <c r="M58" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="N58" t="n">
+        <v>8</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>8</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X58" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.48</v>
       </c>
-      <c r="O58" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P58" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T58" t="n">
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH58" t="n">
         <v>3.3</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X58" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.02</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -8018,47 +8018,47 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="M59" t="n">
         <v>8.5</v>
       </c>
       <c r="N59" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="O59" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
         <v>1.57</v>
@@ -8067,16 +8067,16 @@
         <v>2.25</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AC59" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,19 +8125,19 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G60" t="n">
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.55</v>
+        <v>5.01</v>
       </c>
       <c r="M60" t="n">
-        <v>3.95</v>
+        <v>4.06</v>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>1.58</v>
       </c>
       <c r="O60" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q60" t="n">
         <v>2.15</v>
       </c>
-      <c r="P60" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>4.75</v>
-      </c>
       <c r="R60" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S60" t="n">
         <v>3.2</v>
       </c>
       <c r="T60" t="n">
-        <v>2.68</v>
+        <v>2.35</v>
       </c>
       <c r="U60" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V60" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W60" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X60" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AH60" t="n">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45829.625</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,19 +8254,19 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>5.01</v>
+        <v>1.55</v>
       </c>
       <c r="M61" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="N61" t="n">
-        <v>1.58</v>
+        <v>5</v>
       </c>
       <c r="O61" t="n">
-        <v>4.35</v>
+        <v>2.15</v>
       </c>
       <c r="P61" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.15</v>
+        <v>4.75</v>
       </c>
       <c r="R61" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S61" t="n">
         <v>3.2</v>
       </c>
       <c r="T61" t="n">
-        <v>2.35</v>
+        <v>2.68</v>
       </c>
       <c r="U61" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V61" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W61" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X61" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AD61" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45829.625</v>
@@ -8631,32 +8631,32 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>1</v>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['39', '52', '103']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['26', '76']</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45829.66666666666</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,25 +8770,25 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>5.79</v>
+        <v>3.2</v>
       </c>
       <c r="M65" t="n">
-        <v>4.52</v>
+        <v>3.55</v>
       </c>
       <c r="N65" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB65" t="n">
         <v>1.45</v>
       </c>
-      <c r="O65" t="n">
-        <v>5</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X65" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC65" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['30', '48', '72']</t>
+          <t>['54', '69', '79']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AI65" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45829.66666666666</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,25 +8899,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.2</v>
+        <v>5.79</v>
       </c>
       <c r="M66" t="n">
-        <v>3.55</v>
+        <v>4.52</v>
       </c>
       <c r="N66" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="O66" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="P66" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.64</v>
+        <v>1.9</v>
       </c>
       <c r="R66" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S66" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="T66" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="U66" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="V66" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W66" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X66" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>['54', '69', '79']</t>
+          <t>['30', '48', '72']</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AI66" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45829.66666666666</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,25 +9028,25 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="M67" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O67" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="P67" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q67" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="R67" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S67" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T67" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="V67" t="n">
         <v>1.01</v>
       </c>
       <c r="W67" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X67" t="n">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['58', '70', '9004']</t>
+          <t>['40', '45', '53', '68', '82']</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AH67" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AJ67" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45829.66666666666</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9175,7 +9175,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -9183,83 +9183,83 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="M68" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="O68" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="P68" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="Q68" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X68" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA68" t="n">
         <v>3.9</v>
       </c>
-      <c r="R68" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S68" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T68" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X68" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AB68" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC68" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>['26', '76']</t>
+          <t>['57', '90']</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AI68" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ68" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45829.66666666666</v>
@@ -9276,35 +9276,35 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -9312,83 +9312,83 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['39', '52', '103']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>['57', '90']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45829.66666666666</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,25 +9415,25 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -9441,83 +9441,83 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="N70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O70" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="P70" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="R70" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T70" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="U70" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="V70" t="n">
         <v>1.01</v>
       </c>
       <c r="W70" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X70" t="n">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AD70" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['40', '45', '53', '68', '82']</t>
+          <t>['58', '70', '9004']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AH70" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AJ70" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45829.66666666666</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,25 +10189,25 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -10215,83 +10215,83 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="M76" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="O76" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P76" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T76" t="n">
         <v>2.8</v>
       </c>
-      <c r="P76" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T76" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U76" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V76" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W76" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X76" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AA76" t="n">
         <v>3.6</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '64']</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['29', '45']</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>45829.77083333334</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,25 +10318,25 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -10344,83 +10344,83 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N77" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="P77" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="R77" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S77" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="T77" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U77" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="V77" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W77" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X77" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AA77" t="n">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>['50', '64']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>['29', '45']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AI77" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AJ77" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45829.77083333334</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,25 +10447,25 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -10473,83 +10473,83 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N78" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O78" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q78" t="n">
         <v>3.6</v>
       </c>
-      <c r="O78" t="n">
-        <v>3</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>4.33</v>
-      </c>
       <c r="R78" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S78" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="T78" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="U78" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="V78" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W78" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X78" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AA78" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>['45+10', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>['44', '90+2']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AJ78" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>45829.77083333334</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,25 +10576,25 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -10602,83 +10602,83 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M79" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O79" t="n">
+        <v>3</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S79" t="n">
         <v>2.38</v>
       </c>
-      <c r="P79" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>4</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S79" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T79" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="U79" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="V79" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W79" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="X79" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.48</v>
+        <v>5</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AD79" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['45+10', '67']</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['44', '90+2']</t>
         </is>
       </c>
       <c r="AG79" t="n">
         <v>1.26</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ79" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK79" s="3" t="n">
         <v>45829.77083333334</v>
@@ -10963,25 +10963,25 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -10989,83 +10989,83 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="M82" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="N82" t="n">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="O82" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="P82" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S82" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X82" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA82" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q82" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R82" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S82" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T82" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U82" t="n">
+      <c r="AB82" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC82" t="n">
         <v>1.6</v>
       </c>
-      <c r="V82" t="n">
-        <v>1</v>
-      </c>
-      <c r="W82" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X82" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC82" t="n">
+      <c r="AD82" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>['-1', '-1', '-1', '-1', '-1', '-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>['-1', '-1', '-1', '-1', '-1', '-1', '-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI82" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD82" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>['10', '50', '76', '68']</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>['8', '32', '70']</t>
-        </is>
-      </c>
-      <c r="AG82" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ82" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="AK82" s="3" t="n">
         <v>45829.83333333334</v>
@@ -11221,25 +11221,25 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H84" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -11247,83 +11247,83 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="M84" t="n">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="N84" t="n">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="O84" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="P84" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="R84" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S84" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T84" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U84" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X84" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB84" t="n">
         <v>1.55</v>
       </c>
-      <c r="V84" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W84" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X84" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AC84" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1', '-1', '-1', '-1', '-1']</t>
+          <t>['10', '50', '76', '68']</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1', '-1', '-1', '-1', '-1', '-1']</t>
+          <t>['8', '32', '70']</t>
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AJ84" t="n">
-        <v>2.75</v>
+        <v>2.11</v>
       </c>
       <c r="AK84" s="3" t="n">
         <v>45829.83333333334</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,23 +11479,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
         <v>2</v>
       </c>
-      <c r="I86" t="n">
-        <v>1</v>
-      </c>
       <c r="J86" t="n">
         <v>1</v>
       </c>
@@ -11505,83 +11505,83 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.89</v>
+        <v>1.38</v>
       </c>
       <c r="M86" t="n">
-        <v>3.71</v>
+        <v>4.78</v>
       </c>
       <c r="N86" t="n">
-        <v>2.12</v>
+        <v>6</v>
       </c>
       <c r="O86" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="P86" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.7</v>
+        <v>6.5</v>
       </c>
       <c r="R86" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S86" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T86" t="n">
         <v>2.25</v>
       </c>
       <c r="U86" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V86" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W86" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X86" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="Y86" t="n">
         <v>1.57</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD86" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['8', '44', '77', '88']</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>['16', '50']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="AI86" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AJ86" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="AK86" s="3" t="n">
         <v>45829.85416666666</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,22 +11737,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>1</v>
@@ -11763,83 +11763,83 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.38</v>
+        <v>2.89</v>
       </c>
       <c r="M88" t="n">
-        <v>4.78</v>
+        <v>3.71</v>
       </c>
       <c r="N88" t="n">
-        <v>6</v>
+        <v>2.12</v>
       </c>
       <c r="O88" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="P88" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q88" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
       <c r="R88" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S88" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T88" t="n">
         <v>2.25</v>
       </c>
       <c r="U88" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V88" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W88" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X88" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="Y88" t="n">
         <v>1.57</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>['8', '44', '77', '88']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['16', '50']</t>
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AH88" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="AK88" s="3" t="n">
         <v>45829.85416666666</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,22 +12124,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -12150,83 +12150,83 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="M91" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N91" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O91" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="P91" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R91" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="S91" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="T91" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="U91" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V91" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W91" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="X91" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AA91" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AD91" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG91" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AJ91" t="n">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="AK91" s="3" t="n">
         <v>45829.875</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,19 +12253,19 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -12279,83 +12279,83 @@
         </is>
       </c>
       <c r="L92" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M92" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N92" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O92" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P92" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S92" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T92" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V92" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W92" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X92" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG92" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH92" t="n">
         <v>1.83</v>
       </c>
-      <c r="M92" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N92" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O92" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P92" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R92" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S92" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T92" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U92" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V92" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W92" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X92" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC92" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD92" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AG92" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH92" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AI92" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AJ92" t="n">
-        <v>2.38</v>
+        <v>3.32</v>
       </c>
       <c r="AK92" s="3" t="n">
         <v>45829.875</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,22 +12511,22 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -12537,83 +12537,83 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="O94" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="P94" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S94" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T94" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V94" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X94" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG94" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH94" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q94" t="n">
-        <v>4</v>
-      </c>
-      <c r="R94" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S94" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T94" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U94" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V94" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W94" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X94" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG94" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AI94" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AJ94" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AK94" s="3" t="n">
         <v>45829.875</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,25 +12769,25 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G96" t="n">
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -12795,83 +12795,83 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.7</v>
+        <v>1.36</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="N96" t="n">
-        <v>2.37</v>
+        <v>7.1</v>
       </c>
       <c r="O96" t="n">
-        <v>3.28</v>
+        <v>1.83</v>
       </c>
       <c r="P96" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="R96" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S96" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T96" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="U96" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V96" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W96" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X96" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="Z96" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AB96" t="n">
         <v>1.37</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>['15', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.27</v>
+        <v>2.9</v>
       </c>
       <c r="AI96" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="AJ96" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="AK96" s="3" t="n">
         <v>45829.95833333334</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,25 +12898,25 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G97" t="n">
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -12924,83 +12924,83 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="M97" t="n">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>7.1</v>
+        <v>2.37</v>
       </c>
       <c r="O97" t="n">
-        <v>1.83</v>
+        <v>3.28</v>
       </c>
       <c r="P97" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S97" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T97" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q97" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R97" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S97" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T97" t="n">
-        <v>2.43</v>
-      </c>
       <c r="U97" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V97" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W97" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X97" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AB97" t="n">
         <v>1.37</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '56']</t>
         </is>
       </c>
       <c r="AG97" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AH97" t="n">
-        <v>2.9</v>
+        <v>1.27</v>
       </c>
       <c r="AI97" t="n">
-        <v>1.3</v>
+        <v>1.84</v>
       </c>
       <c r="AJ97" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="AK97" s="3" t="n">
         <v>45829.95833333334</v>
